--- a/Resources/Sheet/Test2.xlsx
+++ b/Resources/Sheet/Test2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C417D1-D394-4A97-9196-B3E1B8B64DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3628289-A4C2-48F2-B701-9990F900AB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QSTBKT" sheetId="1" r:id="rId1"/>
@@ -569,6 +569,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -584,21 +596,9 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -891,84 +891,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:32">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
     </row>
     <row r="4" spans="1:32" ht="33.6" customHeight="1">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:32">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="40"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1306,21 +1306,21 @@
       <c r="AF19" s="12"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="39"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="22"/>
       <c r="S20" s="12"/>
@@ -1339,21 +1339,21 @@
       <c r="AF20" s="12"/>
     </row>
     <row r="21" spans="1:32" ht="18.45" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="15"/>
       <c r="S21" s="16"/>
@@ -1372,23 +1372,23 @@
       <c r="AF21" s="16"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
       <c r="Q22" s="14"/>
       <c r="R22" s="15"/>
       <c r="S22" s="16"/>
@@ -1407,31 +1407,31 @@
       <c r="AF22" s="16"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="40"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1650,84 +1650,84 @@
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="39"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="39"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
     </row>
     <row r="38" spans="1:15" ht="18.45" customHeight="1">
-      <c r="A38" s="39"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="34"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="40"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="40"/>
-      <c r="B41" s="40"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="40"/>
+      <c r="H41" s="35"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -1923,84 +1923,84 @@
       <c r="O51" s="21"/>
     </row>
     <row r="52" spans="1:15" ht="18.45" customHeight="1">
-      <c r="A52" s="39"/>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="34"/>
+      <c r="M52" s="34"/>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
     </row>
     <row r="53" spans="1:15">
-      <c r="A53" s="39"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="34"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="42"/>
-      <c r="O54" s="42"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="40"/>
+      <c r="H56" s="35"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -2122,84 +2122,84 @@
       <c r="O62" s="21"/>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" s="39"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
-      <c r="L63" s="39"/>
-      <c r="M63" s="39"/>
-      <c r="N63" s="39"/>
-      <c r="O63" s="39"/>
+      <c r="A63" s="34"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="34"/>
+      <c r="M63" s="34"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" s="39"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="39"/>
-      <c r="M64" s="39"/>
-      <c r="N64" s="39"/>
-      <c r="O64" s="39"/>
+      <c r="A64" s="34"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="34"/>
+      <c r="L64" s="34"/>
+      <c r="M64" s="34"/>
+      <c r="N64" s="34"/>
+      <c r="O64" s="34"/>
     </row>
     <row r="65" spans="1:15">
-      <c r="A65" s="40" t="s">
+      <c r="A65" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="40"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="40"/>
-      <c r="J65" s="40"/>
-      <c r="K65" s="40"/>
-      <c r="L65" s="40"/>
-      <c r="M65" s="40"/>
-      <c r="N65" s="42"/>
-      <c r="O65" s="42"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="35"/>
+      <c r="M65" s="35"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
     </row>
     <row r="66" spans="1:15">
-      <c r="A66" s="40"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="40"/>
-      <c r="J66" s="40"/>
-      <c r="K66" s="40"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
     </row>
     <row r="67" spans="1:15">
-      <c r="A67" s="40"/>
-      <c r="B67" s="40"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="40"/>
+      <c r="H67" s="35"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -2463,6 +2463,38 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A1:O2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A20:O21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="A37:O38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="A52:O53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="C54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="I55:K55"/>
     <mergeCell ref="A63:O64"/>
     <mergeCell ref="A65:A67"/>
     <mergeCell ref="B65:B67"/>
@@ -2471,38 +2503,6 @@
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="H66:H67"/>
     <mergeCell ref="I66:K66"/>
-    <mergeCell ref="A52:O53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="C54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="A37:O38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="A20:O21"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:M22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="A1:O2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2531,42 +2531,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="42" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="34" t="s">
+      <c r="K1" s="39"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="36"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>10</v>
       </c>
@@ -2619,23 +2619,23 @@
         <v>8</v>
       </c>
       <c r="E3" s="30">
-        <f t="shared" ref="E3:E12" si="0">ROUND(I3*0.5,0)</f>
+        <f>ROUND(C3*D3/2,0)</f>
         <v>0</v>
       </c>
       <c r="F3" s="30">
-        <f t="shared" ref="F3:F12" si="1">ROUND(I3*0.25,0)</f>
+        <f>ROUND(C3*D3/4,0)</f>
         <v>0</v>
       </c>
       <c r="G3" s="30">
-        <f t="shared" ref="G3:G12" si="2">ROUND(I3*0.15,0)</f>
+        <f>ROUND(C3*D3*15/100,0)</f>
         <v>0</v>
       </c>
       <c r="H3" s="30">
-        <f t="shared" ref="H3:H12" si="3">I3-E3-F3-G3</f>
+        <f t="shared" ref="H3:H12" si="0">I3-E3-F3-G3</f>
         <v>0</v>
       </c>
       <c r="I3" s="30">
-        <f t="shared" ref="I3:I12" si="4">ROUND(C3*D3/100,0)</f>
+        <f t="shared" ref="I3:I12" si="1">ROUND(C3*D3/100,0)</f>
         <v>0</v>
       </c>
       <c r="J3" s="31"/>
@@ -2649,15 +2649,15 @@
         <v>0</v>
       </c>
       <c r="N3" s="32">
-        <f t="shared" ref="N3:P12" si="5">F3</f>
+        <f t="shared" ref="N3:P12" si="2">F3</f>
         <v>0</v>
       </c>
       <c r="O3" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P3" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2676,23 +2676,23 @@
         <v>10</v>
       </c>
       <c r="E4" s="30">
+        <f t="shared" ref="E4:E12" si="3">ROUND(C4*D4/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" ref="F4:F12" si="4">ROUND(C4*D4/4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="30">
+        <f t="shared" ref="G4:G12" si="5">ROUND(C4*D4*15/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="30">
+      <c r="I4" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J4" s="33"/>
@@ -2706,15 +2706,15 @@
         <v>0</v>
       </c>
       <c r="N4" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O4" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P4" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2733,23 +2733,23 @@
         <v>4</v>
       </c>
       <c r="E5" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="30">
+      <c r="I5" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J5" s="31"/>
@@ -2763,15 +2763,15 @@
         <v>0</v>
       </c>
       <c r="N5" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O5" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P5" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2790,23 +2790,23 @@
         <v>4</v>
       </c>
       <c r="E6" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="I6" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J6" s="31"/>
@@ -2820,15 +2820,15 @@
         <v>0</v>
       </c>
       <c r="N6" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O6" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P6" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2847,23 +2847,23 @@
         <v>4</v>
       </c>
       <c r="E7" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="I7" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J7" s="31"/>
@@ -2877,15 +2877,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O7" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P7" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2904,23 +2904,23 @@
         <v>4</v>
       </c>
       <c r="E8" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="I8" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J8" s="31"/>
@@ -2934,15 +2934,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O8" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P8" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2961,23 +2961,23 @@
         <v>4</v>
       </c>
       <c r="E9" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="I9" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J9" s="33"/>
@@ -2991,15 +2991,15 @@
         <v>0</v>
       </c>
       <c r="N9" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P9" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3018,23 +3018,23 @@
         <v>10</v>
       </c>
       <c r="E10" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="30">
+      <c r="I10" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J10" s="31"/>
@@ -3048,15 +3048,15 @@
         <v>0</v>
       </c>
       <c r="N10" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P10" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3075,23 +3075,23 @@
         <v>10</v>
       </c>
       <c r="E11" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="30">
+      <c r="I11" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J11" s="31"/>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="N11" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P11" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3132,23 +3132,23 @@
         <v>10</v>
       </c>
       <c r="E12" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="I12" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J12" s="31"/>
@@ -3162,15 +3162,15 @@
         <v>0</v>
       </c>
       <c r="N12" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P12" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
